--- a/assets/file/revalgo_data.xlsx
+++ b/assets/file/revalgo_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>qty_requested</t>
   </si>
@@ -61,9 +61,6 @@
     <t>housing_material</t>
   </si>
   <si>
-    <t>Product img</t>
-  </si>
-  <si>
     <t>ID4667734</t>
   </si>
   <si>
@@ -86,6 +83,12 @@
   </si>
   <si>
     <t>non-metallic</t>
+  </si>
+  <si>
+    <t>product_img</t>
+  </si>
+  <si>
+    <t>default_thumbnail_image</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
     <col min="6" max="6" width="11.140625" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" customWidth="1"/>
     <col min="15" max="15" width="16.85546875" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -498,7 +501,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>56</v>
@@ -522,10 +525,10 @@
         <v>7843279</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2">
         <v>13</v>
@@ -534,10 +537,10 @@
         <v>6</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P2">
         <v>77</v>
@@ -548,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>97</v>
@@ -572,10 +575,10 @@
         <v>9886849</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>9</v>
@@ -584,10 +587,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" t="s">
         <v>22</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
       </c>
       <c r="P3">
         <v>87</v>
